--- a/banco_tabajara.xlsx
+++ b/banco_tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Paulo </t>
+          <t>João Paulo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Salario</t>
+          <t xml:space="preserve">Salario </t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -481,12 +481,44 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Paloma Silva</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Corrente</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>46364045808</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>401</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>
